--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650629</t>
+          <t xml:space="preserve">311650588</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650619</t>
+          <t xml:space="preserve">311650588</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650606</t>
+          <t xml:space="preserve">311650588</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650662</t>
+          <t xml:space="preserve">311652357</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652376</t>
+          <t xml:space="preserve">311652357</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">

--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:L39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Reberbanen 58</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100015361</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>491</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Markgade 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">5480347</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>649</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Markgade 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">5480347</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>365</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Markgade 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">5480347</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>785</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">5480375</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>352</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tordenskjoldsgade 20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">5481018</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>718</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>678</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 22B</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>644</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevejen 40</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>332</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">734262, 7828151</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>342</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">734264, 5481257</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">60</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>711</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnepladsen 2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">734268, 5481265</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">58</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>397</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 48C</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">734281, 5482498</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>376</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 48C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">734281, 5482498</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>326</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pakhusvej 3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">734295, 7828151</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>297</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitsø 1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5985</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">734314, 5074611</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>664</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">St. Rise Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">734316, 5072879</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>1062</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vråvejen 16C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">734335, 7403913</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>1201</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">7125841</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>352</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">200031208</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 32</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">5481279</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1454</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">200047026</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 16B</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">8279514</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>397</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">200048884</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-05-06</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">5482154</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>5417</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311519677</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statene 2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">1355910</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>3366</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311558148</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statene 6</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503780</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>632</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311558150</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sygehusvejen 33B</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503798</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>315</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311558147</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gasværksvej 6</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5481241</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>393</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311614197</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ellenet 10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5482816</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>3153</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311614100</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ellenet 10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5482816</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>318</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311620606</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">St. Rise Skolevej 3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">5072876</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>915</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311650588</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">St. Rise Skolevej 3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5072876</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>1222</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311650588</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">St. Rise Skolevej 3</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">5072876</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>257</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311650588</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærøskøbing Havn 4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503437</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>431</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311652357</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ærøskøbing Havn 4A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503437</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>717</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311652357</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statene 40</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503715</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>355</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311760253</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statene 42</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503715</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1616</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311760254</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statene 44</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5970</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">5503715</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>837</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311760258</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 22</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">734278, 5482154</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1078</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311766361</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-06-13</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,39 +2311,49 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkestræde 23</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5960</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">5480514</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>284</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311877761</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-21</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:L39"/>
 </worksheet>
 </file>
--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reberbanen 58</t>
+          <t xml:space="preserve">Halvejen 20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100015361</t>
+          <t xml:space="preserve">5482154</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H2">
-        <v>491</v>
+        <v>678</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markgade 1</t>
+          <t xml:space="preserve">Halvejen 22B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5480347</t>
+          <t xml:space="preserve">5482154</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H3">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markgade 1</t>
+          <t xml:space="preserve">Havnegade 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5480347</t>
+          <t xml:space="preserve">734262, 7828151</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H4">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markgade 1</t>
+          <t xml:space="preserve">Havnegade 11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5480347</t>
+          <t xml:space="preserve">734264, 5481257</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="H5">
-        <v>785</v>
+        <v>711</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 28</t>
+          <t xml:space="preserve">Havnepladsen 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5480375</t>
+          <t xml:space="preserve">734268, 5481265</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="H6">
-        <v>352</v>
+        <v>397</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tordenskjoldsgade 20</t>
+          <t xml:space="preserve">Markgade 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,7 +401,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5481018</t>
+          <t xml:space="preserve">5480347</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -410,7 +410,7 @@
         </is>
       </c>
       <c r="H7">
-        <v>718</v>
+        <v>649</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 20</t>
+          <t xml:space="preserve">Markgade 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5482154</t>
+          <t xml:space="preserve">5480347</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H8">
-        <v>678</v>
+        <v>365</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 22B</t>
+          <t xml:space="preserve">Markgade 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5482154</t>
+          <t xml:space="preserve">5480347</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H9">
-        <v>644</v>
+        <v>785</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 1</t>
+          <t xml:space="preserve">Pakhusvej 3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">734262, 7828151</t>
+          <t xml:space="preserve">734295, 7828151</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H11">
-        <v>342</v>
+        <v>297</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 11</t>
+          <t xml:space="preserve">Reberbanen 58</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">734264, 5481257</t>
+          <t xml:space="preserve">100015361</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>711</v>
+        <v>491</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 2</t>
+          <t xml:space="preserve">Skolegade 28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">734268, 5481265</t>
+          <t xml:space="preserve">5480375</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 48C</t>
+          <t xml:space="preserve">St. Rise Skolevej 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5960</t>
+          <t xml:space="preserve">5970</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">734281, 5482498</t>
+          <t xml:space="preserve">734316, 5072879</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H14">
-        <v>376</v>
+        <v>1062</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 48C</t>
+          <t xml:space="preserve">Tordenskjoldsgade 20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">734281, 5482498</t>
+          <t xml:space="preserve">5481018</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H15">
-        <v>326</v>
+        <v>718</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pakhusvej 3</t>
+          <t xml:space="preserve">Vestergade 48C</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">734295, 7828151</t>
+          <t xml:space="preserve">734281, 5482498</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>297</v>
+        <v>376</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitsø 1</t>
+          <t xml:space="preserve">Vestergade 48C</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5985</t>
+          <t xml:space="preserve">5960</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">734314, 5074611</t>
+          <t xml:space="preserve">734281, 5482498</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H17">
-        <v>664</v>
+        <v>326</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">St. Rise Skolevej 1</t>
+          <t xml:space="preserve">Vitsø 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5970</t>
+          <t xml:space="preserve">5985</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">734316, 5072879</t>
+          <t xml:space="preserve">734314, 5074611</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18">
-        <v>1062</v>
+        <v>664</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 6</t>
+          <t xml:space="preserve">Ellenet 10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5481241</t>
+          <t xml:space="preserve">5482816</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="H27">
-        <v>393</v>
+        <v>3153</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614197</t>
+          <t xml:space="preserve">311614100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellenet 10</t>
+          <t xml:space="preserve">Gasværksvej 6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5482816</t>
+          <t xml:space="preserve">5481241</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,11 +1670,11 @@
         </is>
       </c>
       <c r="H28">
-        <v>3153</v>
+        <v>393</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614100</t>
+          <t xml:space="preserve">311614197</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650588</t>
+          <t xml:space="preserve">311650629</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650588</t>
+          <t xml:space="preserve">311650619</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650588</t>
+          <t xml:space="preserve">311650606</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652357</t>
+          <t xml:space="preserve">311652376</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650619</t>
+          <t xml:space="preserve">311650588</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">

--- a/public/exports/28856075.xlsx
+++ b/public/exports/28856075.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:M39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Kolding)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Kolding)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Odense)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-05-06</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-12</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1794,20 +1939,25 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650629</t>
+          <t xml:space="preserve">311650588</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1914,20 +2069,25 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650606</t>
+          <t xml:space="preserve">311650588</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2034,20 +2199,25 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652376</t>
+          <t xml:space="preserve">311652357</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-05-17</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-13</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,21 +2529,26 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-21</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L39"/>
+  <autoFilter ref="A1:M39"/>
 </worksheet>
 </file>